--- a/07_Data_Structures/05_FileHandling/FileHandlingUsingExcelFile/WriteData.xlsx
+++ b/07_Data_Structures/05_FileHandling/FileHandlingUsingExcelFile/WriteData.xlsx
@@ -413,18 +413,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Name </t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Profession</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Age</t>
         </is>
       </c>
     </row>
@@ -434,8 +439,15 @@
           <t>Zafrin</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>25</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SQA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hello</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -444,19 +456,77 @@
           <t>Joya</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>26</v>
-      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SQA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Zoei</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>27</v>
-      </c>
+          <t>Tanvir</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SQA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Diya</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SQA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Towa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SQA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Afrin</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SQA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tajrian</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SQA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
